--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_apoyopot_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_apoyopot_a_2020_antofagasta.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:08</t>
+    <t xml:space="preserve">2026-09-24 00:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -941,13 +941,13 @@
         <v>9</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="20">
@@ -964,13 +964,13 @@
         <v>9</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="21">
@@ -990,7 +990,7 @@
         <v>-0.08</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0.25</v>
